--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127338384</v>
+        <v>127340359</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>91345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577622</v>
+        <v>577553</v>
       </c>
       <c r="R2" t="n">
-        <v>6313721</v>
+        <v>6313436</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +743,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,61 +770,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127338314</v>
+        <v>127342351</v>
       </c>
       <c r="B3" t="n">
-        <v>91744</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577644</v>
+        <v>577491</v>
       </c>
       <c r="R3" t="n">
-        <v>6313732</v>
+        <v>6313525</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127338535</v>
+        <v>127343235</v>
       </c>
       <c r="B4" t="n">
         <v>57654</v>
@@ -907,16 +913,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577587</v>
+        <v>577617</v>
       </c>
       <c r="R4" t="n">
-        <v>6313721</v>
+        <v>6313742</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,24 +957,9 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår i träd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127338604</v>
+        <v>127338384</v>
       </c>
       <c r="B5" t="n">
-        <v>79632</v>
+        <v>57654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,34 +997,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577626</v>
+        <v>577622</v>
       </c>
       <c r="R5" t="n">
-        <v>6313699</v>
+        <v>6313721</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1061,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På stubbe med brandljud</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127338859</v>
+        <v>127341596</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>79632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,42 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577597</v>
+        <v>577512</v>
       </c>
       <c r="R6" t="n">
-        <v>6313684</v>
+        <v>6313425</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,6 +1187,1797 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127341966</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91345</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>577509</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6313498</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127338535</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>577587</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6313721</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår i träd.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127338314</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91744</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577644</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6313732</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127340685</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91345</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>577578</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6313362</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127342562</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>577449</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6313581</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127340680</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91345</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>577598</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6313404</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127342942</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>577485</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6313627</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Pa gammal stubbe med sår av brand.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127339786</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91345</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>577513</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6313472</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fin gammal tallskog. Här finns fler tickor.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127343187</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>577574</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6313730</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127339629</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91345</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>577562</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6313595</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På död stående tall</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127343198</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91345</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>577568</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6313701</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127339864</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91345</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>577503</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6313402</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127338604</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79632</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>577626</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6313699</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På stubbe med brandljud</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127338859</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>577597</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6313684</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127342390</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91345</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>577475</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6313561</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127340404</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91345</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>577525</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6313427</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gammal tall med pansarbark</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127339560</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>577573</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6313587</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127340359</v>
+        <v>127342351</v>
       </c>
       <c r="B2" t="n">
-        <v>91345</v>
+        <v>79632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577553</v>
+        <v>577491</v>
       </c>
       <c r="R2" t="n">
-        <v>6313436</v>
+        <v>6313525</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +743,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:33</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127342351</v>
+        <v>127340359</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>91346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +812,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577491</v>
+        <v>577553</v>
       </c>
       <c r="R3" t="n">
-        <v>6313525</v>
+        <v>6313436</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,14 +845,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1193,7 +1193,7 @@
         <v>127341966</v>
       </c>
       <c r="B7" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>127338314</v>
       </c>
       <c r="B9" t="n">
-        <v>91744</v>
+        <v>91745</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>127340685</v>
       </c>
       <c r="B10" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127340680</v>
+        <v>127339786</v>
       </c>
       <c r="B12" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,19 +1752,24 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577598</v>
+        <v>577513</v>
       </c>
       <c r="R12" t="n">
-        <v>6313404</v>
+        <v>6313472</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1791,9 +1796,24 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fin gammal tallskog. Här finns fler tickor.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1808,12 +1828,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1922,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127339786</v>
+        <v>127340680</v>
       </c>
       <c r="B14" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,24 +1975,19 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577513</v>
+        <v>577598</v>
       </c>
       <c r="R14" t="n">
-        <v>6313472</v>
+        <v>6313404</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1999,24 +2014,9 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Fin gammal tallskog. Här finns fler tickor.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,12 +2031,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2148,7 +2148,7 @@
         <v>127339629</v>
       </c>
       <c r="B16" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127343198</v>
+        <v>127339864</v>
       </c>
       <c r="B17" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577568</v>
+        <v>577503</v>
       </c>
       <c r="R17" t="n">
-        <v>6313701</v>
+        <v>6313402</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2327,12 +2327,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2359,10 +2354,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127339864</v>
+        <v>127343198</v>
       </c>
       <c r="B18" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2394,13 +2389,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577503</v>
+        <v>577568</v>
       </c>
       <c r="R18" t="n">
-        <v>6313402</v>
+        <v>6313701</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2429,7 +2424,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2439,7 +2434,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,7 +2673,7 @@
         <v>127342390</v>
       </c>
       <c r="B21" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>127340404</v>
       </c>
       <c r="B22" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127342351</v>
+        <v>127343235</v>
       </c>
       <c r="B2" t="n">
-        <v>79632</v>
+        <v>57654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577491</v>
+        <v>577617</v>
       </c>
       <c r="R2" t="n">
-        <v>6313525</v>
+        <v>6313742</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127340359</v>
+        <v>127342351</v>
       </c>
       <c r="B3" t="n">
-        <v>91346</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577553</v>
+        <v>577491</v>
       </c>
       <c r="R3" t="n">
-        <v>6313436</v>
+        <v>6313525</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -845,19 +845,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:33</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127343235</v>
+        <v>127340359</v>
       </c>
       <c r="B4" t="n">
-        <v>57654</v>
+        <v>91346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,42 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577617</v>
+        <v>577553</v>
       </c>
       <c r="R4" t="n">
-        <v>6313742</v>
+        <v>6313436</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,9 +947,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,12 +974,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127342351</v>
+        <v>127340359</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>91346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577491</v>
+        <v>577553</v>
       </c>
       <c r="R3" t="n">
-        <v>6313525</v>
+        <v>6313436</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -845,14 +845,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127340359</v>
+        <v>127342351</v>
       </c>
       <c r="B4" t="n">
-        <v>91346</v>
+        <v>79632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577553</v>
+        <v>577491</v>
       </c>
       <c r="R4" t="n">
-        <v>6313436</v>
+        <v>6313525</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,19 +952,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:33</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,12 +974,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127341596</v>
+        <v>127341966</v>
       </c>
       <c r="B6" t="n">
-        <v>79632</v>
+        <v>91346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577512</v>
+        <v>577509</v>
       </c>
       <c r="R6" t="n">
-        <v>6313425</v>
+        <v>6313498</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,14 +1156,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127341966</v>
+        <v>127341596</v>
       </c>
       <c r="B7" t="n">
-        <v>91346</v>
+        <v>79632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577509</v>
+        <v>577512</v>
       </c>
       <c r="R7" t="n">
-        <v>6313498</v>
+        <v>6313425</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,19 +1263,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:37</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,57 +1285,61 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127338535</v>
+        <v>127338314</v>
       </c>
       <c r="B8" t="n">
-        <v>57654</v>
+        <v>91745</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577587</v>
+        <v>577644</v>
       </c>
       <c r="R8" t="n">
-        <v>6313721</v>
+        <v>6313732</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,24 +1369,9 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spår i träd.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,61 +1386,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127338314</v>
+        <v>127338535</v>
       </c>
       <c r="B9" t="n">
-        <v>91745</v>
+        <v>57654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577644</v>
+        <v>577587</v>
       </c>
       <c r="R9" t="n">
-        <v>6313732</v>
+        <v>6313721</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,9 +1466,24 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spår i träd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127342942</v>
+        <v>127340680</v>
       </c>
       <c r="B13" t="n">
-        <v>79632</v>
+        <v>91346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,37 +1851,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577485</v>
+        <v>577598</v>
       </c>
       <c r="R13" t="n">
-        <v>6313627</v>
+        <v>6313404</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1911,11 +1915,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127340680</v>
+        <v>127342942</v>
       </c>
       <c r="B14" t="n">
-        <v>91346</v>
+        <v>79632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,41 +1952,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577598</v>
+        <v>577485</v>
       </c>
       <c r="R14" t="n">
-        <v>6313404</v>
+        <v>6313627</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,6 +2012,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127343235</v>
+        <v>127342351</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>79636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577617</v>
+        <v>577491</v>
       </c>
       <c r="R2" t="n">
-        <v>6313742</v>
+        <v>6313525</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +780,7 @@
         <v>127340359</v>
       </c>
       <c r="B3" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127342351</v>
+        <v>127343235</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>57658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577491</v>
+        <v>577617</v>
       </c>
       <c r="R4" t="n">
-        <v>6313525</v>
+        <v>6313742</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,7 +989,7 @@
         <v>127338384</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127341966</v>
+        <v>127341596</v>
       </c>
       <c r="B6" t="n">
-        <v>91346</v>
+        <v>79636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577509</v>
+        <v>577512</v>
       </c>
       <c r="R6" t="n">
-        <v>6313498</v>
+        <v>6313425</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,19 +1156,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:37</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127341596</v>
+        <v>127341966</v>
       </c>
       <c r="B7" t="n">
-        <v>79632</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577512</v>
+        <v>577509</v>
       </c>
       <c r="R7" t="n">
-        <v>6313425</v>
+        <v>6313498</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1263,14 +1258,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,12 +1285,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
         <v>127338314</v>
       </c>
       <c r="B8" t="n">
-        <v>91745</v>
+        <v>91749</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>127338535</v>
       </c>
       <c r="B9" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>127340685</v>
       </c>
       <c r="B10" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>127342562</v>
       </c>
       <c r="B11" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>127339786</v>
       </c>
       <c r="B12" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127340680</v>
+        <v>127342942</v>
       </c>
       <c r="B13" t="n">
-        <v>91346</v>
+        <v>79636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,41 +1851,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577598</v>
+        <v>577485</v>
       </c>
       <c r="R13" t="n">
-        <v>6313404</v>
+        <v>6313627</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1915,6 +1911,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1941,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127342942</v>
+        <v>127340680</v>
       </c>
       <c r="B14" t="n">
-        <v>79632</v>
+        <v>91350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,37 +1953,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577485</v>
+        <v>577598</v>
       </c>
       <c r="R14" t="n">
-        <v>6313627</v>
+        <v>6313404</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2012,11 +2017,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +2046,7 @@
         <v>127343187</v>
       </c>
       <c r="B15" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>127339629</v>
       </c>
       <c r="B16" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127339864</v>
       </c>
       <c r="B17" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>127343198</v>
       </c>
       <c r="B18" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>127338604</v>
       </c>
       <c r="B19" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>127338859</v>
       </c>
       <c r="B20" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>127342390</v>
       </c>
       <c r="B21" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>127340404</v>
       </c>
       <c r="B22" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>127339560</v>
       </c>
       <c r="B23" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127342351</v>
+        <v>127343235</v>
       </c>
       <c r="B2" t="n">
-        <v>79636</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577491</v>
+        <v>577617</v>
       </c>
       <c r="R2" t="n">
-        <v>6313525</v>
+        <v>6313742</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127343235</v>
+        <v>127342351</v>
       </c>
       <c r="B4" t="n">
-        <v>57658</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,39 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577617</v>
+        <v>577491</v>
       </c>
       <c r="R4" t="n">
-        <v>6313742</v>
+        <v>6313525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127341596</v>
+        <v>127341966</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577512</v>
+        <v>577509</v>
       </c>
       <c r="R6" t="n">
-        <v>6313425</v>
+        <v>6313498</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,14 +1156,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127341966</v>
+        <v>127341596</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577509</v>
+        <v>577512</v>
       </c>
       <c r="R7" t="n">
-        <v>6313498</v>
+        <v>6313425</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,19 +1263,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:37</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,61 +1285,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127338314</v>
+        <v>127338535</v>
       </c>
       <c r="B8" t="n">
-        <v>91749</v>
+        <v>57658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577644</v>
+        <v>577587</v>
       </c>
       <c r="R8" t="n">
-        <v>6313732</v>
+        <v>6313721</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,9 +1365,24 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår i träd.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1386,57 +1397,61 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127338535</v>
+        <v>127338314</v>
       </c>
       <c r="B9" t="n">
-        <v>57658</v>
+        <v>91749</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577587</v>
+        <v>577644</v>
       </c>
       <c r="R9" t="n">
-        <v>6313721</v>
+        <v>6313732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,24 +1481,9 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spår i träd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127342942</v>
+        <v>127340680</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,37 +1851,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577485</v>
+        <v>577598</v>
       </c>
       <c r="R13" t="n">
-        <v>6313627</v>
+        <v>6313404</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1911,11 +1915,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127340680</v>
+        <v>127342942</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,41 +1952,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577598</v>
+        <v>577485</v>
       </c>
       <c r="R14" t="n">
-        <v>6313404</v>
+        <v>6313627</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,6 +2012,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2247,7 +2247,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127339864</v>
+        <v>127343198</v>
       </c>
       <c r="B17" t="n">
         <v>91350</v>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577503</v>
+        <v>577568</v>
       </c>
       <c r="R17" t="n">
-        <v>6313402</v>
+        <v>6313701</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2327,7 +2327,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2354,7 +2359,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127343198</v>
+        <v>127339864</v>
       </c>
       <c r="B18" t="n">
         <v>91350</v>
@@ -2389,13 +2394,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577568</v>
+        <v>577503</v>
       </c>
       <c r="R18" t="n">
-        <v>6313701</v>
+        <v>6313402</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2424,7 +2429,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2434,12 +2439,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127343235</v>
+        <v>127342351</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>79636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577617</v>
+        <v>577491</v>
       </c>
       <c r="R2" t="n">
-        <v>6313742</v>
+        <v>6313525</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127340359</v>
+        <v>127343235</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +788,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577553</v>
+        <v>577617</v>
       </c>
       <c r="R3" t="n">
-        <v>6313436</v>
+        <v>6313742</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -845,19 +850,9 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127342351</v>
+        <v>127340359</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +914,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577491</v>
+        <v>577553</v>
       </c>
       <c r="R4" t="n">
-        <v>6313525</v>
+        <v>6313436</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,14 +947,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,12 +974,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127342351</v>
+        <v>127343235</v>
       </c>
       <c r="B2" t="n">
-        <v>79636</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577491</v>
+        <v>577617</v>
       </c>
       <c r="R2" t="n">
-        <v>6313525</v>
+        <v>6313742</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127343235</v>
+        <v>127340359</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,42 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577617</v>
+        <v>577553</v>
       </c>
       <c r="R3" t="n">
-        <v>6313742</v>
+        <v>6313436</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,9 +845,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127340359</v>
+        <v>127342351</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577553</v>
+        <v>577491</v>
       </c>
       <c r="R4" t="n">
-        <v>6313436</v>
+        <v>6313525</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,19 +952,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:33</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,12 +974,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127343235</v>
+        <v>127340359</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>91350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577617</v>
+        <v>577553</v>
       </c>
       <c r="R2" t="n">
-        <v>6313742</v>
+        <v>6313436</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +743,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127340359</v>
+        <v>127342351</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577553</v>
+        <v>577491</v>
       </c>
       <c r="R3" t="n">
-        <v>6313436</v>
+        <v>6313525</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -845,19 +850,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:33</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127342351</v>
+        <v>127343235</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>57658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577491</v>
+        <v>577617</v>
       </c>
       <c r="R4" t="n">
-        <v>6313525</v>
+        <v>6313742</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127341966</v>
+        <v>127341596</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577509</v>
+        <v>577512</v>
       </c>
       <c r="R6" t="n">
-        <v>6313498</v>
+        <v>6313425</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,19 +1156,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:37</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127341596</v>
+        <v>127341966</v>
       </c>
       <c r="B7" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577512</v>
+        <v>577509</v>
       </c>
       <c r="R7" t="n">
-        <v>6313425</v>
+        <v>6313498</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1263,14 +1258,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,57 +1285,61 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127338535</v>
+        <v>127338314</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>91749</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577587</v>
+        <v>577644</v>
       </c>
       <c r="R8" t="n">
-        <v>6313721</v>
+        <v>6313732</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,24 +1369,9 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spår i träd.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,61 +1386,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127338314</v>
+        <v>127338535</v>
       </c>
       <c r="B9" t="n">
-        <v>91749</v>
+        <v>57658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577644</v>
+        <v>577587</v>
       </c>
       <c r="R9" t="n">
-        <v>6313732</v>
+        <v>6313721</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,9 +1466,24 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spår i träd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2247,7 +2247,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127343198</v>
+        <v>127339864</v>
       </c>
       <c r="B17" t="n">
         <v>91350</v>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577568</v>
+        <v>577503</v>
       </c>
       <c r="R17" t="n">
-        <v>6313701</v>
+        <v>6313402</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2327,12 +2327,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2359,7 +2354,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127339864</v>
+        <v>127343198</v>
       </c>
       <c r="B18" t="n">
         <v>91350</v>
@@ -2394,13 +2389,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577503</v>
+        <v>577568</v>
       </c>
       <c r="R18" t="n">
-        <v>6313402</v>
+        <v>6313701</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2429,7 +2424,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2439,7 +2434,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127341596</v>
+        <v>127341966</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577512</v>
+        <v>577509</v>
       </c>
       <c r="R6" t="n">
-        <v>6313425</v>
+        <v>6313498</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,14 +1156,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127341966</v>
+        <v>127341596</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577509</v>
+        <v>577512</v>
       </c>
       <c r="R7" t="n">
-        <v>6313498</v>
+        <v>6313425</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,19 +1263,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:37</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,12 +1285,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127339786</v>
+        <v>127342942</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>79636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,46 +1730,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577513</v>
+        <v>577485</v>
       </c>
       <c r="R12" t="n">
-        <v>6313472</v>
+        <v>6313627</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,24 +1787,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fin gammal tallskog. Här finns fler tickor.</t>
+          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1828,19 +1809,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127340680</v>
+        <v>127339786</v>
       </c>
       <c r="B13" t="n">
         <v>91350</v>
@@ -1873,19 +1854,24 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577598</v>
+        <v>577513</v>
       </c>
       <c r="R13" t="n">
-        <v>6313404</v>
+        <v>6313472</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1912,9 +1898,24 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Fin gammal tallskog. Här finns fler tickor.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,22 +1930,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127342942</v>
+        <v>127340680</v>
       </c>
       <c r="B14" t="n">
-        <v>79636</v>
+        <v>91350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,37 +1953,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577485</v>
+        <v>577598</v>
       </c>
       <c r="R14" t="n">
-        <v>6313627</v>
+        <v>6313404</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2012,11 +2017,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127340359</v>
+        <v>127342351</v>
       </c>
       <c r="B2" t="n">
-        <v>91350</v>
+        <v>79638</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577553</v>
+        <v>577491</v>
       </c>
       <c r="R2" t="n">
-        <v>6313436</v>
+        <v>6313525</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +743,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:33</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127342351</v>
+        <v>127340359</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>91352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +812,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577491</v>
+        <v>577553</v>
       </c>
       <c r="R3" t="n">
-        <v>6313525</v>
+        <v>6313436</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,14 +845,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -887,7 +887,7 @@
         <v>127343235</v>
       </c>
       <c r="B4" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127338384</v>
       </c>
       <c r="B5" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127341966</v>
+        <v>127341596</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>79638</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577509</v>
+        <v>577512</v>
       </c>
       <c r="R6" t="n">
-        <v>6313498</v>
+        <v>6313425</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,19 +1156,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:37</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127341596</v>
+        <v>127341966</v>
       </c>
       <c r="B7" t="n">
-        <v>79636</v>
+        <v>91352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577512</v>
+        <v>577509</v>
       </c>
       <c r="R7" t="n">
-        <v>6313425</v>
+        <v>6313498</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1263,14 +1258,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,12 +1285,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
         <v>127338314</v>
       </c>
       <c r="B8" t="n">
-        <v>91749</v>
+        <v>91751</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>127338535</v>
       </c>
       <c r="B9" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>127340685</v>
       </c>
       <c r="B10" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>127342562</v>
       </c>
       <c r="B11" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127342942</v>
+        <v>127339786</v>
       </c>
       <c r="B12" t="n">
-        <v>79636</v>
+        <v>91352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,37 +1730,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577485</v>
+        <v>577513</v>
       </c>
       <c r="R12" t="n">
-        <v>6313627</v>
+        <v>6313472</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1787,14 +1796,24 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Pa gammal stubbe med sår av brand.</t>
+          <t>Fin gammal tallskog. Här finns fler tickor.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,22 +1828,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127339786</v>
+        <v>127342942</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>79638</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,46 +1851,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577513</v>
+        <v>577485</v>
       </c>
       <c r="R13" t="n">
-        <v>6313472</v>
+        <v>6313627</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1898,24 +1908,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fin gammal tallskog. Här finns fler tickor.</t>
+          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1930,12 +1930,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
         <v>127340680</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>127343187</v>
       </c>
       <c r="B15" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>127339629</v>
       </c>
       <c r="B16" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127339864</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>127343198</v>
       </c>
       <c r="B18" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>127338604</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>127338859</v>
       </c>
       <c r="B20" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>127342390</v>
       </c>
       <c r="B21" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>127340404</v>
       </c>
       <c r="B22" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>127339560</v>
       </c>
       <c r="B23" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127342351</v>
+        <v>127340359</v>
       </c>
       <c r="B2" t="n">
-        <v>79638</v>
+        <v>91352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577491</v>
+        <v>577553</v>
       </c>
       <c r="R2" t="n">
-        <v>6313525</v>
+        <v>6313436</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,14 +743,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127340359</v>
+        <v>127343235</v>
       </c>
       <c r="B3" t="n">
-        <v>91352</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577553</v>
+        <v>577617</v>
       </c>
       <c r="R3" t="n">
-        <v>6313436</v>
+        <v>6313742</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -845,19 +855,9 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127343235</v>
+        <v>127342351</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,39 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577617</v>
+        <v>577491</v>
       </c>
       <c r="R4" t="n">
-        <v>6313742</v>
+        <v>6313525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127341596</v>
+        <v>127341966</v>
       </c>
       <c r="B6" t="n">
-        <v>79638</v>
+        <v>91352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577512</v>
+        <v>577509</v>
       </c>
       <c r="R6" t="n">
-        <v>6313425</v>
+        <v>6313498</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,14 +1156,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127341966</v>
+        <v>127341596</v>
       </c>
       <c r="B7" t="n">
-        <v>91352</v>
+        <v>79638</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577509</v>
+        <v>577512</v>
       </c>
       <c r="R7" t="n">
-        <v>6313498</v>
+        <v>6313425</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,19 +1263,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:37</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,12 +1285,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127342942</v>
+        <v>127340680</v>
       </c>
       <c r="B13" t="n">
-        <v>79638</v>
+        <v>91352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,37 +1851,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577485</v>
+        <v>577598</v>
       </c>
       <c r="R13" t="n">
-        <v>6313627</v>
+        <v>6313404</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1911,11 +1915,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127340680</v>
+        <v>127342942</v>
       </c>
       <c r="B14" t="n">
-        <v>91352</v>
+        <v>79638</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,41 +1952,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577598</v>
+        <v>577485</v>
       </c>
       <c r="R14" t="n">
-        <v>6313404</v>
+        <v>6313627</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,6 +2012,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2247,7 +2247,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127339864</v>
+        <v>127343198</v>
       </c>
       <c r="B17" t="n">
         <v>91352</v>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577503</v>
+        <v>577568</v>
       </c>
       <c r="R17" t="n">
-        <v>6313402</v>
+        <v>6313701</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2327,7 +2327,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2354,7 +2359,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127343198</v>
+        <v>127339864</v>
       </c>
       <c r="B18" t="n">
         <v>91352</v>
@@ -2389,13 +2394,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577568</v>
+        <v>577503</v>
       </c>
       <c r="R18" t="n">
-        <v>6313701</v>
+        <v>6313402</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2424,7 +2429,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2434,12 +2439,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127343235</v>
+        <v>127342351</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577617</v>
+        <v>577491</v>
       </c>
       <c r="R3" t="n">
-        <v>6313742</v>
+        <v>6313525</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127342351</v>
+        <v>127343235</v>
       </c>
       <c r="B4" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577491</v>
+        <v>577617</v>
       </c>
       <c r="R4" t="n">
-        <v>6313525</v>
+        <v>6313742</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127340359</v>
+        <v>127342351</v>
       </c>
       <c r="B2" t="n">
-        <v>91352</v>
+        <v>79638</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577553</v>
+        <v>577491</v>
       </c>
       <c r="R2" t="n">
-        <v>6313436</v>
+        <v>6313525</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +743,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:33</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127342351</v>
+        <v>127340359</v>
       </c>
       <c r="B3" t="n">
-        <v>79638</v>
+        <v>91352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +812,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577491</v>
+        <v>577553</v>
       </c>
       <c r="R3" t="n">
-        <v>6313525</v>
+        <v>6313436</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,14 +845,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127341966</v>
+        <v>127341596</v>
       </c>
       <c r="B6" t="n">
-        <v>91352</v>
+        <v>79638</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577509</v>
+        <v>577512</v>
       </c>
       <c r="R6" t="n">
-        <v>6313498</v>
+        <v>6313425</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,19 +1156,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:37</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127341596</v>
+        <v>127341966</v>
       </c>
       <c r="B7" t="n">
-        <v>79638</v>
+        <v>91352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577512</v>
+        <v>577509</v>
       </c>
       <c r="R7" t="n">
-        <v>6313425</v>
+        <v>6313498</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1263,14 +1258,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,12 +1285,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127340680</v>
+        <v>127342942</v>
       </c>
       <c r="B13" t="n">
-        <v>91352</v>
+        <v>79638</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,41 +1851,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577598</v>
+        <v>577485</v>
       </c>
       <c r="R13" t="n">
-        <v>6313404</v>
+        <v>6313627</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1915,6 +1911,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1941,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127342942</v>
+        <v>127340680</v>
       </c>
       <c r="B14" t="n">
-        <v>79638</v>
+        <v>91352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,37 +1953,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577485</v>
+        <v>577598</v>
       </c>
       <c r="R14" t="n">
-        <v>6313627</v>
+        <v>6313404</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2012,11 +2017,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2247,7 +2247,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127343198</v>
+        <v>127339864</v>
       </c>
       <c r="B17" t="n">
         <v>91352</v>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577568</v>
+        <v>577503</v>
       </c>
       <c r="R17" t="n">
-        <v>6313701</v>
+        <v>6313402</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2327,12 +2327,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2359,7 +2354,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127339864</v>
+        <v>127343198</v>
       </c>
       <c r="B18" t="n">
         <v>91352</v>
@@ -2394,13 +2389,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577503</v>
+        <v>577568</v>
       </c>
       <c r="R18" t="n">
-        <v>6313402</v>
+        <v>6313701</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2429,7 +2424,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2439,7 +2434,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127340359</v>
       </c>
       <c r="B3" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127341596</v>
+        <v>127341966</v>
       </c>
       <c r="B6" t="n">
-        <v>79638</v>
+        <v>91358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577512</v>
+        <v>577509</v>
       </c>
       <c r="R6" t="n">
-        <v>6313425</v>
+        <v>6313498</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,14 +1156,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127341966</v>
+        <v>127341596</v>
       </c>
       <c r="B7" t="n">
-        <v>91352</v>
+        <v>79638</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577509</v>
+        <v>577512</v>
       </c>
       <c r="R7" t="n">
-        <v>6313498</v>
+        <v>6313425</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,19 +1263,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:37</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,61 +1285,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127338314</v>
+        <v>127338535</v>
       </c>
       <c r="B8" t="n">
-        <v>91751</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577644</v>
+        <v>577587</v>
       </c>
       <c r="R8" t="n">
-        <v>6313732</v>
+        <v>6313721</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,9 +1365,24 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår i träd.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1386,57 +1397,61 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127338535</v>
+        <v>127338314</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>91757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577587</v>
+        <v>577644</v>
       </c>
       <c r="R9" t="n">
-        <v>6313721</v>
+        <v>6313732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,24 +1481,9 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spår i träd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1513,7 +1513,7 @@
         <v>127340685</v>
       </c>
       <c r="B10" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127339786</v>
+        <v>127342942</v>
       </c>
       <c r="B12" t="n">
-        <v>91352</v>
+        <v>79638</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,46 +1730,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577513</v>
+        <v>577485</v>
       </c>
       <c r="R12" t="n">
-        <v>6313472</v>
+        <v>6313627</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,24 +1787,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fin gammal tallskog. Här finns fler tickor.</t>
+          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1828,22 +1809,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127342942</v>
+        <v>127339786</v>
       </c>
       <c r="B13" t="n">
-        <v>79638</v>
+        <v>91358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,37 +1832,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577485</v>
+        <v>577513</v>
       </c>
       <c r="R13" t="n">
-        <v>6313627</v>
+        <v>6313472</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1908,14 +1898,24 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Pa gammal stubbe med sår av brand.</t>
+          <t>Fin gammal tallskog. Här finns fler tickor.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1930,12 +1930,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
         <v>127340680</v>
       </c>
       <c r="B14" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>127339629</v>
       </c>
       <c r="B16" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127339864</v>
       </c>
       <c r="B17" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>127343198</v>
       </c>
       <c r="B18" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>127342390</v>
       </c>
       <c r="B21" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>127340404</v>
       </c>
       <c r="B22" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127342351</v>
       </c>
       <c r="B2" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127340359</v>
+        <v>127343235</v>
       </c>
       <c r="B3" t="n">
-        <v>91358</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +788,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577553</v>
+        <v>577617</v>
       </c>
       <c r="R3" t="n">
-        <v>6313436</v>
+        <v>6313742</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -845,19 +850,9 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127343235</v>
+        <v>127340359</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>91361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,42 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577617</v>
+        <v>577553</v>
       </c>
       <c r="R4" t="n">
-        <v>6313742</v>
+        <v>6313436</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,9 +947,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,12 +974,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -989,7 +989,7 @@
         <v>127338384</v>
       </c>
       <c r="B5" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127341966</v>
+        <v>127341596</v>
       </c>
       <c r="B6" t="n">
-        <v>91358</v>
+        <v>79641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577509</v>
+        <v>577512</v>
       </c>
       <c r="R6" t="n">
-        <v>6313498</v>
+        <v>6313425</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,19 +1156,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:37</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127341596</v>
+        <v>127341966</v>
       </c>
       <c r="B7" t="n">
-        <v>79638</v>
+        <v>91361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577512</v>
+        <v>577509</v>
       </c>
       <c r="R7" t="n">
-        <v>6313425</v>
+        <v>6313498</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1263,14 +1258,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,12 +1285,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
         <v>127338535</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>127338314</v>
       </c>
       <c r="B9" t="n">
-        <v>91757</v>
+        <v>91760</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>127340685</v>
       </c>
       <c r="B10" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>127342562</v>
       </c>
       <c r="B11" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>127342942</v>
       </c>
       <c r="B12" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>127339786</v>
       </c>
       <c r="B13" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>127340680</v>
       </c>
       <c r="B14" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>127343187</v>
       </c>
       <c r="B15" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>127339629</v>
       </c>
       <c r="B16" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127339864</v>
       </c>
       <c r="B17" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>127343198</v>
       </c>
       <c r="B18" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>127338604</v>
       </c>
       <c r="B19" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>127338859</v>
       </c>
       <c r="B20" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>127342390</v>
       </c>
       <c r="B21" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>127340404</v>
       </c>
       <c r="B22" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>127339560</v>
       </c>
       <c r="B23" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127342351</v>
       </c>
       <c r="B2" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127343235</v>
+        <v>127340359</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>91369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,42 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577617</v>
+        <v>577553</v>
       </c>
       <c r="R3" t="n">
-        <v>6313742</v>
+        <v>6313436</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,9 +845,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127340359</v>
+        <v>127343235</v>
       </c>
       <c r="B4" t="n">
-        <v>91361</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,37 +895,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577553</v>
+        <v>577617</v>
       </c>
       <c r="R4" t="n">
-        <v>6313436</v>
+        <v>6313742</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,19 +957,9 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,12 +974,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -989,7 +989,7 @@
         <v>127338384</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>127341596</v>
       </c>
       <c r="B6" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>127341966</v>
       </c>
       <c r="B7" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,45 +1297,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127338535</v>
+        <v>127338314</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>91768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577587</v>
+        <v>577644</v>
       </c>
       <c r="R8" t="n">
-        <v>6313721</v>
+        <v>6313732</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,24 +1369,9 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spår i träd.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,61 +1386,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127338314</v>
+        <v>127338535</v>
       </c>
       <c r="B9" t="n">
-        <v>91760</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577644</v>
+        <v>577587</v>
       </c>
       <c r="R9" t="n">
-        <v>6313732</v>
+        <v>6313721</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,9 +1466,24 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spår i träd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,12 +1498,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1513,7 +1513,7 @@
         <v>127340685</v>
       </c>
       <c r="B10" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>127342562</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127342942</v>
+        <v>127339786</v>
       </c>
       <c r="B12" t="n">
-        <v>79641</v>
+        <v>91369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,37 +1730,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577485</v>
+        <v>577513</v>
       </c>
       <c r="R12" t="n">
-        <v>6313627</v>
+        <v>6313472</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1787,14 +1796,24 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Pa gammal stubbe med sår av brand.</t>
+          <t>Fin gammal tallskog. Här finns fler tickor.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,22 +1828,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127339786</v>
+        <v>127342942</v>
       </c>
       <c r="B13" t="n">
-        <v>91361</v>
+        <v>79647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,46 +1851,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577513</v>
+        <v>577485</v>
       </c>
       <c r="R13" t="n">
-        <v>6313472</v>
+        <v>6313627</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1898,24 +1908,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fin gammal tallskog. Här finns fler tickor.</t>
+          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1930,12 +1930,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
         <v>127340680</v>
       </c>
       <c r="B14" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>127343187</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>127339629</v>
       </c>
       <c r="B16" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127339864</v>
       </c>
       <c r="B17" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>127343198</v>
       </c>
       <c r="B18" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>127338604</v>
       </c>
       <c r="B19" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>127338859</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>127342390</v>
       </c>
       <c r="B21" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>127340404</v>
       </c>
       <c r="B22" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>127339560</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127342351</v>
+        <v>127340359</v>
       </c>
       <c r="B2" t="n">
-        <v>79647</v>
+        <v>91370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577491</v>
+        <v>577553</v>
       </c>
       <c r="R2" t="n">
-        <v>6313525</v>
+        <v>6313436</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,14 +743,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127340359</v>
+        <v>127342351</v>
       </c>
       <c r="B3" t="n">
-        <v>91369</v>
+        <v>79647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577553</v>
+        <v>577491</v>
       </c>
       <c r="R3" t="n">
-        <v>6313436</v>
+        <v>6313525</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -845,19 +850,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:33</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127341596</v>
+        <v>127341966</v>
       </c>
       <c r="B6" t="n">
-        <v>79647</v>
+        <v>91370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577512</v>
+        <v>577509</v>
       </c>
       <c r="R6" t="n">
-        <v>6313425</v>
+        <v>6313498</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,14 +1156,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127341966</v>
+        <v>127341596</v>
       </c>
       <c r="B7" t="n">
-        <v>91369</v>
+        <v>79647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577509</v>
+        <v>577512</v>
       </c>
       <c r="R7" t="n">
-        <v>6313498</v>
+        <v>6313425</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,19 +1263,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:37</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,12 +1285,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
         <v>127338314</v>
       </c>
       <c r="B8" t="n">
-        <v>91768</v>
+        <v>91769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>127340685</v>
       </c>
       <c r="B10" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>127339786</v>
       </c>
       <c r="B12" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127342942</v>
+        <v>127340680</v>
       </c>
       <c r="B13" t="n">
-        <v>79647</v>
+        <v>91370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,37 +1851,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577485</v>
+        <v>577598</v>
       </c>
       <c r="R13" t="n">
-        <v>6313627</v>
+        <v>6313404</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1911,11 +1915,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127340680</v>
+        <v>127342942</v>
       </c>
       <c r="B14" t="n">
-        <v>91369</v>
+        <v>79647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,41 +1952,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577598</v>
+        <v>577485</v>
       </c>
       <c r="R14" t="n">
-        <v>6313404</v>
+        <v>6313627</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,6 +2012,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2148,7 @@
         <v>127339629</v>
       </c>
       <c r="B16" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127339864</v>
       </c>
       <c r="B17" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>127343198</v>
       </c>
       <c r="B18" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>127342390</v>
       </c>
       <c r="B21" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>127340404</v>
       </c>
       <c r="B22" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127340359</v>
+        <v>127342351</v>
       </c>
       <c r="B2" t="n">
-        <v>91370</v>
+        <v>79647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577553</v>
+        <v>577491</v>
       </c>
       <c r="R2" t="n">
-        <v>6313436</v>
+        <v>6313525</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +743,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:33</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127342351</v>
+        <v>127340359</v>
       </c>
       <c r="B3" t="n">
-        <v>79647</v>
+        <v>91370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +812,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577491</v>
+        <v>577553</v>
       </c>
       <c r="R3" t="n">
-        <v>6313525</v>
+        <v>6313436</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,14 +845,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127339786</v>
+        <v>127342942</v>
       </c>
       <c r="B12" t="n">
-        <v>91370</v>
+        <v>79647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,46 +1730,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577513</v>
+        <v>577485</v>
       </c>
       <c r="R12" t="n">
-        <v>6313472</v>
+        <v>6313627</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,24 +1787,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fin gammal tallskog. Här finns fler tickor.</t>
+          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1828,19 +1809,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127340680</v>
+        <v>127339786</v>
       </c>
       <c r="B13" t="n">
         <v>91370</v>
@@ -1873,19 +1854,24 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577598</v>
+        <v>577513</v>
       </c>
       <c r="R13" t="n">
-        <v>6313404</v>
+        <v>6313472</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1912,9 +1898,24 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Fin gammal tallskog. Här finns fler tickor.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,22 +1930,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127342942</v>
+        <v>127340680</v>
       </c>
       <c r="B14" t="n">
-        <v>79647</v>
+        <v>91370</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,37 +1953,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577485</v>
+        <v>577598</v>
       </c>
       <c r="R14" t="n">
-        <v>6313627</v>
+        <v>6313404</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2012,11 +2017,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2247,7 +2247,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127339864</v>
+        <v>127343198</v>
       </c>
       <c r="B17" t="n">
         <v>91370</v>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577503</v>
+        <v>577568</v>
       </c>
       <c r="R17" t="n">
-        <v>6313402</v>
+        <v>6313701</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2327,7 +2327,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2354,7 +2359,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127343198</v>
+        <v>127339864</v>
       </c>
       <c r="B18" t="n">
         <v>91370</v>
@@ -2389,13 +2394,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577568</v>
+        <v>577503</v>
       </c>
       <c r="R18" t="n">
-        <v>6313701</v>
+        <v>6313402</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2424,7 +2429,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2434,12 +2439,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127340359</v>
       </c>
       <c r="B3" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>127341966</v>
       </c>
       <c r="B6" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127338314</v>
       </c>
       <c r="B8" t="n">
-        <v>91769</v>
+        <v>91770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>127340685</v>
       </c>
       <c r="B10" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127342942</v>
+        <v>127339786</v>
       </c>
       <c r="B12" t="n">
-        <v>79647</v>
+        <v>91371</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,37 +1730,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577485</v>
+        <v>577513</v>
       </c>
       <c r="R12" t="n">
-        <v>6313627</v>
+        <v>6313472</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1787,14 +1796,24 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Pa gammal stubbe med sår av brand.</t>
+          <t>Fin gammal tallskog. Här finns fler tickor.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,22 +1828,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127339786</v>
+        <v>127340680</v>
       </c>
       <c r="B13" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,24 +1873,19 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577513</v>
+        <v>577598</v>
       </c>
       <c r="R13" t="n">
-        <v>6313472</v>
+        <v>6313404</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1898,24 +1912,9 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Fin gammal tallskog. Här finns fler tickor.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1930,22 +1929,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127340680</v>
+        <v>127342942</v>
       </c>
       <c r="B14" t="n">
-        <v>91370</v>
+        <v>79647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,41 +1952,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577598</v>
+        <v>577485</v>
       </c>
       <c r="R14" t="n">
-        <v>6313404</v>
+        <v>6313627</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,6 +2012,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2148,7 @@
         <v>127339629</v>
       </c>
       <c r="B16" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127343198</v>
+        <v>127339864</v>
       </c>
       <c r="B17" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577568</v>
+        <v>577503</v>
       </c>
       <c r="R17" t="n">
-        <v>6313701</v>
+        <v>6313402</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2327,12 +2327,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2359,10 +2354,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127339864</v>
+        <v>127343198</v>
       </c>
       <c r="B18" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2394,13 +2389,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577503</v>
+        <v>577568</v>
       </c>
       <c r="R18" t="n">
-        <v>6313402</v>
+        <v>6313701</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2429,7 +2424,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2439,7 +2434,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,7 +2673,7 @@
         <v>127342390</v>
       </c>
       <c r="B21" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>127340404</v>
       </c>
       <c r="B22" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127340359</v>
       </c>
       <c r="B3" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127341966</v>
+        <v>127341596</v>
       </c>
       <c r="B6" t="n">
-        <v>91371</v>
+        <v>79647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577509</v>
+        <v>577512</v>
       </c>
       <c r="R6" t="n">
-        <v>6313498</v>
+        <v>6313425</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,19 +1156,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:37</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127341596</v>
+        <v>127341966</v>
       </c>
       <c r="B7" t="n">
-        <v>79647</v>
+        <v>91372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577512</v>
+        <v>577509</v>
       </c>
       <c r="R7" t="n">
-        <v>6313425</v>
+        <v>6313498</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1263,14 +1258,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,12 +1285,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
         <v>127338314</v>
       </c>
       <c r="B8" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>127340685</v>
       </c>
       <c r="B10" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127339786</v>
+        <v>127342942</v>
       </c>
       <c r="B12" t="n">
-        <v>91371</v>
+        <v>79647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,46 +1730,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577513</v>
+        <v>577485</v>
       </c>
       <c r="R12" t="n">
-        <v>6313472</v>
+        <v>6313627</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,24 +1787,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fin gammal tallskog. Här finns fler tickor.</t>
+          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1828,22 +1809,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127340680</v>
+        <v>127339786</v>
       </c>
       <c r="B13" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,19 +1854,24 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577598</v>
+        <v>577513</v>
       </c>
       <c r="R13" t="n">
-        <v>6313404</v>
+        <v>6313472</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1912,9 +1898,24 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Fin gammal tallskog. Här finns fler tickor.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,22 +1930,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127342942</v>
+        <v>127340680</v>
       </c>
       <c r="B14" t="n">
-        <v>79647</v>
+        <v>91372</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,37 +1953,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577485</v>
+        <v>577598</v>
       </c>
       <c r="R14" t="n">
-        <v>6313627</v>
+        <v>6313404</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2012,11 +2017,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2148,7 @@
         <v>127339629</v>
       </c>
       <c r="B16" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>127339864</v>
       </c>
       <c r="B17" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>127343198</v>
       </c>
       <c r="B18" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>127342390</v>
       </c>
       <c r="B21" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>127340404</v>
       </c>
       <c r="B22" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127342351</v>
+        <v>127338314</v>
       </c>
       <c r="B2" t="n">
-        <v>79647</v>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577491</v>
+        <v>577644</v>
       </c>
       <c r="R2" t="n">
-        <v>6313525</v>
+        <v>6313732</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127340359</v>
+        <v>127339629</v>
       </c>
       <c r="B3" t="n">
-        <v>91372</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,13 +811,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577553</v>
+        <v>577562</v>
       </c>
       <c r="R3" t="n">
-        <v>6313436</v>
+        <v>6313595</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -845,19 +844,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:33</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På död stående tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +866,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127343235</v>
+        <v>127339786</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,27 +889,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -924,13 +922,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577617</v>
+        <v>577513</v>
       </c>
       <c r="R4" t="n">
-        <v>6313742</v>
+        <v>6313472</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,9 +955,24 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fin gammal tallskog. Här finns fler tickor.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,22 +987,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127338384</v>
+        <v>127339864</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,42 +1010,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577622</v>
+        <v>577503</v>
       </c>
       <c r="R5" t="n">
-        <v>6313721</v>
+        <v>6313402</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1059,9 +1067,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,22 +1094,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127341596</v>
+        <v>127340359</v>
       </c>
       <c r="B6" t="n">
-        <v>79647</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1141,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577512</v>
+        <v>577553</v>
       </c>
       <c r="R6" t="n">
-        <v>6313425</v>
+        <v>6313436</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,14 +1174,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal stubbe med spår av brand</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,22 +1201,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127341966</v>
+        <v>127340404</v>
       </c>
       <c r="B7" t="n">
-        <v>91372</v>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,13 +1248,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577509</v>
+        <v>577525</v>
       </c>
       <c r="R7" t="n">
-        <v>6313498</v>
+        <v>6313427</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,19 +1281,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:37</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal tall med pansarbark</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,49 +1303,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127338314</v>
+        <v>127340680</v>
       </c>
       <c r="B8" t="n">
-        <v>91771</v>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1336,13 +1354,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577644</v>
+        <v>577598</v>
       </c>
       <c r="R8" t="n">
-        <v>6313732</v>
+        <v>6313404</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1398,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127338535</v>
+        <v>127340685</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,21 +1427,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,13 +1451,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577587</v>
+        <v>577578</v>
       </c>
       <c r="R9" t="n">
-        <v>6313721</v>
+        <v>6313362</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1468,7 +1486,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1478,12 +1496,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spår i träd.</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127340685</v>
+        <v>127341966</v>
       </c>
       <c r="B10" t="n">
-        <v>91372</v>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1545,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577578</v>
+        <v>577509</v>
       </c>
       <c r="R10" t="n">
-        <v>6313362</v>
+        <v>6313498</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1580,7 +1593,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1590,7 +1603,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127342562</v>
+        <v>127342390</v>
       </c>
       <c r="B11" t="n">
-        <v>57669</v>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,42 +1641,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577449</v>
+        <v>577475</v>
       </c>
       <c r="R11" t="n">
-        <v>6313581</v>
+        <v>6313561</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1690,9 +1698,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1707,22 +1725,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127342942</v>
+        <v>127343198</v>
       </c>
       <c r="B12" t="n">
-        <v>79647</v>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,21 +1748,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,13 +1772,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577485</v>
+        <v>577568</v>
       </c>
       <c r="R12" t="n">
-        <v>6313627</v>
+        <v>6313701</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1787,14 +1805,24 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Pa gammal stubbe med sår av brand.</t>
+          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,22 +1837,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Kristian  Norrby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127339786</v>
+        <v>127338604</v>
       </c>
       <c r="B13" t="n">
-        <v>91372</v>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,46 +1860,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577513</v>
+        <v>577626</v>
       </c>
       <c r="R13" t="n">
-        <v>6313472</v>
+        <v>6313699</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1898,24 +1917,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fin gammal tallskog. Här finns fler tickor.</t>
+          <t>På stubbe med brandljud</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1930,22 +1939,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127340680</v>
+        <v>127341596</v>
       </c>
       <c r="B14" t="n">
-        <v>91372</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,41 +1962,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577598</v>
+        <v>577512</v>
       </c>
       <c r="R14" t="n">
-        <v>6313404</v>
+        <v>6313425</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,6 +2022,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2043,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127343187</v>
+        <v>127342351</v>
       </c>
       <c r="B15" t="n">
-        <v>57669</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2054,39 +2064,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577574</v>
+        <v>577491</v>
       </c>
       <c r="R15" t="n">
-        <v>6313730</v>
+        <v>6313525</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,6 +2124,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gammal stubbe med spår av brand</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2145,10 +2155,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127339629</v>
+        <v>127342942</v>
       </c>
       <c r="B16" t="n">
-        <v>91372</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2156,21 +2166,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2180,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577562</v>
+        <v>577485</v>
       </c>
       <c r="R16" t="n">
-        <v>6313595</v>
+        <v>6313627</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,7 +2230,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På död stående tall</t>
+          <t>Pa gammal stubbe med sår av brand.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2247,48 +2257,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127339864</v>
+        <v>127338384</v>
       </c>
       <c r="B17" t="n">
-        <v>91372</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577503</v>
+        <v>577622</v>
       </c>
       <c r="R17" t="n">
-        <v>6313402</v>
+        <v>6313721</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2315,19 +2330,9 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,44 +2347,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127343198</v>
+        <v>127338535</v>
       </c>
       <c r="B18" t="n">
-        <v>91372</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2389,13 +2394,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577568</v>
+        <v>577587</v>
       </c>
       <c r="R18" t="n">
-        <v>6313701</v>
+        <v>6313721</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2424,7 +2429,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2434,12 +2439,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Två fina ex. Här finns ca 15 tal tallar med tickor på. I gammal skog som snart skall avverkas.</t>
+          <t>Spår i träd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2466,45 +2471,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127338604</v>
+        <v>127338859</v>
       </c>
       <c r="B19" t="n">
-        <v>79647</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577626</v>
+        <v>577597</v>
       </c>
       <c r="R19" t="n">
-        <v>6313699</v>
+        <v>6313684</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2537,11 +2547,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På stubbe med brandljud</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2568,14 +2573,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127338859</v>
+        <v>127339560</v>
       </c>
       <c r="B20" t="n">
-        <v>57669</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2608,10 +2613,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577597</v>
+        <v>577573</v>
       </c>
       <c r="R20" t="n">
-        <v>6313684</v>
+        <v>6313587</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2670,48 +2675,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127342390</v>
+        <v>127339856</v>
       </c>
       <c r="B21" t="n">
-        <v>91372</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577475</v>
+        <v>577595</v>
       </c>
       <c r="R21" t="n">
-        <v>6313561</v>
+        <v>6313541</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2738,19 +2748,9 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2765,60 +2765,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127340404</v>
+        <v>127342562</v>
       </c>
       <c r="B22" t="n">
-        <v>91372</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brinkekärret, Brinkekärret, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577525</v>
+        <v>577449</v>
       </c>
       <c r="R22" t="n">
-        <v>6313427</v>
+        <v>6313581</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2848,11 +2853,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gammal tall med pansarbark</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2879,14 +2879,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127339560</v>
+        <v>127343187</v>
       </c>
       <c r="B23" t="n">
-        <v>57669</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2919,13 +2919,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577573</v>
+        <v>577574</v>
       </c>
       <c r="R23" t="n">
-        <v>6313587</v>
+        <v>6313730</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2978,6 +2978,108 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127343235</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Brinkekärret, Brinkekärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>577617</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6313742</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33105-2025 artfynd.xlsx
+++ b/artfynd/A 33105-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127338314</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127339629</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127339786</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127339864</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127340359</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127340404</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,6 +1448,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127340680</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127340685</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1627,6 +1672,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127341966</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1734,6 +1784,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127342390</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1846,6 +1901,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127343198</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1948,6 +2008,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127338604</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127341596</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2152,6 +2222,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127342351</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2254,6 +2329,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127342942</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2356,6 +2436,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127338384</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2468,6 +2553,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127338535</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2570,6 +2660,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127338859</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2672,6 +2767,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127339560</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2774,6 +2874,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127339856</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2876,6 +2981,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127342562</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2978,6 +3088,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127343187</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3080,8 +3195,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127343235</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>